--- a/legal_forms/005_divorce_mediation_checklist--legal_forms.xlsx
+++ b/legal_forms/005_divorce_mediation_checklist--legal_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'phone',_'value':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Phone', 'value': 'phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'email',_'value':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Email', 'value': 'email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'in_person',_'value':_'in_person'}</t>
+          <t>in_person</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'In Person', 'value': 'in_person'}</t>
+          <t>In Person</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'ready',_'value':_true}</t>
+          <t>ready</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Ready', 'value': True}</t>
+          <t>Ready</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'not_ready',_'value':_false}</t>
+          <t>not_ready</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Not Ready', 'value': False}</t>
+          <t>Not Ready</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'continue_with_session',_'value':_'continue_session'}</t>
+          <t>continue_with_session</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Continue with Session', 'value': 'continue_session'}</t>
+          <t>Continue with Session</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'end_session',_'value':_'end_session'}</t>
+          <t>end_session</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'End Session', 'value': 'end_session'}</t>
+          <t>End Session</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
